--- a/data/LCL FREIGHT.xlsx
+++ b/data/LCL FREIGHT.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIA" sheetId="2" r:id="R396b9bbdbc42409e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHINA" sheetId="3" r:id="Rf34106203d584690"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="N.CHINA" sheetId="4" r:id="R84d9c79d8d614e72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S.CHINA" sheetId="5" r:id="R53fa69ac1e874288"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JAPAN" sheetId="6" r:id="R38a01799b192428c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EUROPE" sheetId="7" r:id="R2d3bbf599f644c51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MEDSEA" sheetId="8" r:id="R32cb517192a741ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AFRICA" sheetId="9" r:id="R27fddce1a28843a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S.AMERICA" sheetId="21" r:id="R1009cca32e5a4000"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="N.AMERICA" sheetId="16" r:id="Rdccb65b9856741d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OCEANIA" sheetId="15" r:id="R8830a3e37ca64dc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MIDEAST " sheetId="14" r:id="Red0cecd822e24cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ASIA" sheetId="2" r:id="Rae03160e6b19410b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHINA" sheetId="3" r:id="R6e2691b8363e480a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="N.CHINA" sheetId="4" r:id="Rd047ad49a986408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S.CHINA" sheetId="5" r:id="R8c912c1f90404f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JAPAN" sheetId="6" r:id="R3140a63fc4ec4dce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EUROPE" sheetId="7" r:id="R9d82b6f9c37c40ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MEDSEA" sheetId="8" r:id="R6e672a7502e745eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AFRICA" sheetId="9" r:id="Rb1a0ae2084b84365"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S.AMERICA" sheetId="21" r:id="R25196b3bf08c464a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="N.AMERICA" sheetId="16" r:id="Rf60996922c11485c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OCEANIA" sheetId="15" r:id="R385e89fc2c59496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MIDEAST" sheetId="14" r:id="Rd20cc99315a24ea2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -7079,13 +7079,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image1.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra12303f496304d3f"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5c5f291fcfc54c71"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7116,13 +7116,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image8.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image10.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf058a92101cf48b0"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc878c86cc7964240"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7148,13 +7148,13 @@
     <xdr:ext cx="6625478" cy="1293159"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image9.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image11.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Re7ab565cf0f648f4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Raef077698a154983"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7180,13 +7180,13 @@
     <xdr:ext cx="5766547" cy="1106021"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image10.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image12.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R72f92156e8a94bce"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R094b0eb4bf594029"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7223,7 +7223,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5ae204254b73451a"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2704e031aef540fe"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7254,13 +7254,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image2.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image3.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6b979beb60e74c6f"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1d67fc38fb104c8f"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7291,13 +7291,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image2.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image4.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2267a721bc90439a"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rca3b4babe80b4049"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7328,13 +7328,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image3.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image5.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rb8b9942c355a4ed8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R5a9bd62f5f654ce9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7365,13 +7365,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image4.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image6.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9a008e087a2a48e2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R86a9bfacca28450f"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7402,13 +7402,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image5.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image7.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra68ae2db09544a98"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rca251fe925594b5f"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7439,13 +7439,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image6.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image8.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rae2ac056e1074dd3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R191a28e007a246d2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7471,13 +7471,13 @@
     <xdr:ext cx="7950653" cy="1438275"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="/xl/media/image7.png"/>
+        <xdr:cNvPr id="1" name="/xl/media/image9.png"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R60430475aea54b41"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rde58fa795f3c4271"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -9184,8 +9184,8 @@
     <x:mergeCell ref="C50:D50"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b4d5fb9a5c34de8"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb978442ae8041b5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fe5c1fcc3d34cfa"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7067732b23274354"/>
 </x:worksheet>
 </file>
 
@@ -11794,7 +11794,7 @@
     <x:mergeCell ref="L9:N9"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cd8ba4e57244bf5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R307b8405e26049cf"/>
 </x:worksheet>
 </file>
 
@@ -12805,7 +12805,7 @@
     <x:mergeCell ref="A22:A23"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec43246ff8b842c3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R815a69ab5b9c4c01"/>
 </x:worksheet>
 </file>
 
@@ -13574,7 +13574,7 @@
     <x:mergeCell ref="A33:I33"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re72fafe6813d4afe"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfe6bde3553c44d6"/>
 </x:worksheet>
 </file>
 
@@ -14324,7 +14324,7 @@
     <x:mergeCell ref="A32:H32"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf777dfb117043dd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92f4e2a4fee84484"/>
 </x:worksheet>
 </file>
 
@@ -15794,7 +15794,7 @@
     <x:mergeCell ref="A8:F8"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd211cb4aaad6432a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7721c92e64d84979"/>
 </x:worksheet>
 </file>
 
@@ -16783,7 +16783,7 @@
     <x:mergeCell ref="C19:F19"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86b027fc8f3242ae"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83d559633073445d"/>
 </x:worksheet>
 </file>
 
@@ -17705,8 +17705,8 @@
     <x:mergeCell ref="A42:G42"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc47edc36d504627"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82600be4a19b480d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e71b5dd8f7f4927"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb76c04604ef54897"/>
 </x:worksheet>
 </file>
 
@@ -21472,7 +21472,7 @@
     <x:mergeCell ref="C110:D110"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b103dfa27674572"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf93ab13fda1c4f09"/>
 </x:worksheet>
 </file>
 
@@ -22657,7 +22657,7 @@
     <x:mergeCell ref="A39:A41"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda2eeebb38d747b9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R723138263da447df"/>
 </x:worksheet>
 </file>
 
@@ -24861,7 +24861,7 @@
     <x:mergeCell ref="C56:D56"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6665ba03cfee4fa9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb750d66aaad64baa"/>
 </x:worksheet>
 </file>
 
@@ -29647,6 +29647,6 @@
     <x:mergeCell ref="J15:L15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57fb56ca4d4f48b2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2717043c2994162"/>
 </x:worksheet>
 </file>